--- a/Double_FEDs/DOUBLE_FED_Key.xlsx
+++ b/Double_FEDs/DOUBLE_FED_Key.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2366676637589/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/murrell_wustl_edu/Documents/Documents/Github/PredictingObesity/Double_FEDs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{B9EACA95-5E54-4E38-8229-34EB2087740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03159D49-307B-49AF-A3DE-1CED0B543800}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="8_{B9EACA95-5E54-4E38-8229-34EB2087740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7140EB99-BD95-4555-9517-6D11FAD1A68B}"/>
   <bookViews>
-    <workbookView xWindow="-25125" yWindow="1770" windowWidth="23505" windowHeight="13050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2790" yWindow="735" windowWidth="23505" windowHeight="13050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="117">
   <si>
     <t>filename</t>
   </si>
@@ -456,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -464,15 +464,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,14 +767,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="4"/>
     <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -804,10 +795,10 @@
       <c r="F1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -824,16 +815,16 @@
       <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="3">
         <v>46223</v>
       </c>
-      <c r="H2" s="4" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -850,16 +841,16 @@
       <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="3">
         <v>46223</v>
       </c>
-      <c r="H3" s="4" t="b">
+      <c r="H3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -876,16 +867,16 @@
       <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>46225</v>
       </c>
-      <c r="H4" s="4" t="b">
+      <c r="H4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -902,16 +893,16 @@
       <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="3">
         <v>46223</v>
       </c>
-      <c r="H5" s="4" t="b">
+      <c r="H5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -928,16 +919,16 @@
       <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="3">
         <v>46223</v>
       </c>
-      <c r="H6" s="4" t="b">
+      <c r="H6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -954,16 +945,16 @@
       <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <v>46225</v>
       </c>
-      <c r="H7" s="4" t="b">
+      <c r="H7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -980,16 +971,16 @@
       <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="3">
         <v>46223</v>
       </c>
-      <c r="H8" s="4" t="b">
+      <c r="H8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1006,16 +997,16 @@
       <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="3">
         <v>46245</v>
       </c>
-      <c r="H9" s="4" t="b">
+      <c r="H9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1032,16 +1023,16 @@
       <c r="D10" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="3">
         <v>46247</v>
       </c>
-      <c r="H10" s="4" t="b">
+      <c r="H10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1058,16 +1049,16 @@
       <c r="D11" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="3">
         <v>46230</v>
       </c>
-      <c r="H11" s="4" t="b">
+      <c r="H11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1084,16 +1075,16 @@
       <c r="D12" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="3">
         <v>46245</v>
       </c>
-      <c r="H12" s="4" t="b">
+      <c r="H12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1110,16 +1101,16 @@
       <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="3">
         <v>46245</v>
       </c>
-      <c r="H13" s="4" t="b">
+      <c r="H13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1136,16 +1127,16 @@
       <c r="D14" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="3">
         <v>46247</v>
       </c>
-      <c r="H14" s="4" t="b">
+      <c r="H14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1162,16 +1153,16 @@
       <c r="D15" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="3">
         <v>46245</v>
       </c>
-      <c r="H15" s="4" t="b">
+      <c r="H15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1188,24 +1179,24 @@
       <c r="D16" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="3">
         <v>46230</v>
       </c>
-      <c r="H16" s="4" t="b">
+      <c r="H16" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>6</v>
       </c>
       <c r="C17" t="s">
@@ -1214,24 +1205,24 @@
       <c r="D17" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="3">
         <v>46232</v>
       </c>
-      <c r="H17" s="4" t="b">
+      <c r="H17" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18" t="s">
@@ -1240,24 +1231,24 @@
       <c r="D18" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="3">
         <v>46223</v>
       </c>
-      <c r="H18" s="4" t="b">
+      <c r="H18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" t="s">
         <v>6</v>
       </c>
       <c r="C19" t="s">
@@ -1266,102 +1257,102 @@
       <c r="D19" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" t="s">
         <v>69</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="3">
         <v>46225</v>
       </c>
-      <c r="H19" s="4" t="b">
+      <c r="H19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
         <v>22</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="3">
         <v>46223</v>
       </c>
-      <c r="H20" s="4" t="b">
+      <c r="H20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
         <v>23</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="3">
         <v>46223</v>
       </c>
-      <c r="H21" s="4" t="b">
+      <c r="H21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" t="s">
         <v>23</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="3">
         <v>46225</v>
       </c>
-      <c r="H22" s="4" t="b">
+      <c r="H22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" t="s">
         <v>3</v>
       </c>
       <c r="C23" t="s">
@@ -1370,24 +1361,24 @@
       <c r="D23" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="3">
         <v>46223</v>
       </c>
-      <c r="H23" s="4" t="b">
+      <c r="H23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24" t="s">
@@ -1396,76 +1387,76 @@
       <c r="D24" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" t="s">
         <v>73</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="3">
         <v>46225</v>
       </c>
-      <c r="H24" s="4" t="b">
+      <c r="H24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
         <v>22</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" t="s">
         <v>65</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" t="s">
         <v>75</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="3">
         <v>46223</v>
       </c>
-      <c r="H25" s="4" t="b">
+      <c r="H25" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
         <v>23</v>
       </c>
       <c r="D26" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" t="s">
         <v>65</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" t="s">
         <v>72</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="3">
         <v>46245</v>
       </c>
-      <c r="H26" s="4" t="b">
+      <c r="H26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" t="s">
         <v>6</v>
       </c>
       <c r="C27" t="s">
@@ -1474,50 +1465,50 @@
       <c r="D27" t="s">
         <v>56</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" t="s">
         <v>65</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" t="s">
         <v>72</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="3">
         <v>46247</v>
       </c>
-      <c r="H27" s="4" t="b">
+      <c r="H27" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
         <v>22</v>
       </c>
       <c r="D28" t="s">
         <v>57</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" t="s">
         <v>75</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="3">
         <v>46230</v>
       </c>
-      <c r="H28" s="4" t="b">
+      <c r="H28" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" t="s">
         <v>3</v>
       </c>
       <c r="C29" t="s">
@@ -1526,102 +1517,102 @@
       <c r="D29" t="s">
         <v>58</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" t="s">
         <v>65</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" t="s">
         <v>75</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="3">
         <v>46245</v>
       </c>
-      <c r="H29" s="4" t="b">
+      <c r="H29" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
         <v>22</v>
       </c>
       <c r="D30" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="3">
         <v>46230</v>
       </c>
-      <c r="H30" s="4" t="b">
+      <c r="H30" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
         <v>22</v>
       </c>
       <c r="D31" t="s">
         <v>56</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" t="s">
         <v>65</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" t="s">
         <v>66</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="3">
         <v>46245</v>
       </c>
-      <c r="H31" s="4" t="b">
+      <c r="H31" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
         <v>23</v>
       </c>
       <c r="D32" t="s">
         <v>57</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" t="s">
         <v>65</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" t="s">
         <v>67</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="3">
         <v>46230</v>
       </c>
-      <c r="H32" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" t="s">
         <v>6</v>
       </c>
       <c r="C33" t="s">
@@ -1630,50 +1621,50 @@
       <c r="D33" t="s">
         <v>57</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" t="s">
         <v>65</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" t="s">
         <v>67</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="3">
         <v>46232</v>
       </c>
-      <c r="H33" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
         <v>23</v>
       </c>
       <c r="D34" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" t="s">
         <v>69</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="3">
         <v>46230</v>
       </c>
-      <c r="H34" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" t="s">
         <v>6</v>
       </c>
       <c r="C35" t="s">
@@ -1682,992 +1673,932 @@
       <c r="D35" t="s">
         <v>62</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" t="s">
         <v>65</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" t="s">
         <v>69</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="3">
         <v>46232</v>
       </c>
-      <c r="H35" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
         <v>22</v>
       </c>
       <c r="D36" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" t="s">
         <v>70</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="3">
         <v>46230</v>
       </c>
-      <c r="H36" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="4" t="s">
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
         <v>23</v>
       </c>
       <c r="D37" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" t="s">
         <v>65</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" t="s">
         <v>71</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="3">
         <v>46245</v>
       </c>
-      <c r="H37" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>52</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" t="s">
         <v>23</v>
       </c>
       <c r="D38" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" t="s">
         <v>65</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" t="s">
         <v>71</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="3">
         <v>46247</v>
       </c>
-      <c r="H38" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="4" t="s">
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
         <v>23</v>
       </c>
       <c r="D39" t="s">
         <v>55</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" t="s">
         <v>65</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" t="s">
         <v>72</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="3">
         <v>46230</v>
       </c>
-      <c r="H39" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" t="s">
         <v>23</v>
       </c>
       <c r="D40" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" t="s">
         <v>65</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="3">
         <v>46232</v>
       </c>
-      <c r="H40" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="4" t="str">
-        <f t="shared" ref="C41:C70" si="0">LEFT(A41,4)</f>
-        <v>FED0</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
         <v>76</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" s="4" t="s">
+      <c r="E41" t="s">
+        <v>64</v>
+      </c>
+      <c r="F41" t="s">
         <v>68</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="3">
         <v>46132</v>
       </c>
-      <c r="H41" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F42" s="4" t="s">
+      <c r="E42" t="s">
+        <v>64</v>
+      </c>
+      <c r="F42" t="s">
         <v>68</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="3">
         <v>46134</v>
       </c>
-      <c r="H42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" s="4"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
         <v>76</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F43" s="4" t="s">
+      <c r="E43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" t="s">
         <v>68</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="3">
         <v>46139</v>
       </c>
-      <c r="H43" s="4" t="b">
+      <c r="H43" t="b">
         <v>1</v>
       </c>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="3">
+        <v>46132</v>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" t="s">
+        <v>85</v>
+      </c>
+      <c r="G45" s="3">
+        <v>46134</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="s">
+        <v>76</v>
+      </c>
+      <c r="E46" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" t="s">
+        <v>85</v>
+      </c>
+      <c r="G46" s="3">
+        <v>46139</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" t="s">
+        <v>73</v>
+      </c>
+      <c r="G47" s="3">
+        <v>46132</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" t="s">
+        <v>64</v>
+      </c>
+      <c r="F48" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="3">
+        <v>46134</v>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" s="3">
+        <v>46139</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G50" s="3">
+        <v>46132</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" t="s">
+        <v>86</v>
+      </c>
+      <c r="G51" s="3">
+        <v>46134</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" t="s">
+        <v>86</v>
+      </c>
+      <c r="G52" s="3">
+        <v>46139</v>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53" t="s">
+        <v>64</v>
+      </c>
+      <c r="F53" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="3">
+        <v>46132</v>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" t="s">
+        <v>64</v>
+      </c>
+      <c r="F54" t="s">
+        <v>82</v>
+      </c>
+      <c r="G54" s="3">
+        <v>46134</v>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" t="s">
+        <v>82</v>
+      </c>
+      <c r="G55" s="3">
+        <v>46139</v>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" t="s">
+        <v>72</v>
+      </c>
+      <c r="G56" s="3">
+        <v>46132</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" t="s">
+        <v>64</v>
+      </c>
+      <c r="F57" t="s">
+        <v>72</v>
+      </c>
+      <c r="G57" s="3">
+        <v>46134</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" t="s">
+        <v>64</v>
+      </c>
+      <c r="F58" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" s="3">
+        <v>46139</v>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>102</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" t="s">
+        <v>64</v>
+      </c>
+      <c r="F59" t="s">
+        <v>83</v>
+      </c>
+      <c r="G59" s="3">
+        <v>46132</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>103</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60" t="s">
+        <v>83</v>
+      </c>
+      <c r="G60" s="3">
+        <v>46134</v>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>104</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" t="s">
+        <v>64</v>
+      </c>
+      <c r="F61" t="s">
+        <v>83</v>
+      </c>
+      <c r="G61" s="3">
+        <v>46139</v>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" t="s">
+        <v>80</v>
+      </c>
+      <c r="E62" t="s">
+        <v>64</v>
+      </c>
+      <c r="F62" t="s">
+        <v>84</v>
+      </c>
+      <c r="G62" s="3">
+        <v>46132</v>
+      </c>
+      <c r="H62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" t="s">
+        <v>64</v>
+      </c>
+      <c r="F63" t="s">
+        <v>84</v>
+      </c>
+      <c r="G63" s="3">
+        <v>46134</v>
+      </c>
+      <c r="H63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>22</v>
+      </c>
+      <c r="D64" t="s">
+        <v>80</v>
+      </c>
+      <c r="E64" t="s">
+        <v>64</v>
+      </c>
+      <c r="F64" t="s">
+        <v>84</v>
+      </c>
+      <c r="G64" s="3">
+        <v>46139</v>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>90</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="B65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F44" s="4" t="s">
+      <c r="E65" t="s">
+        <v>64</v>
+      </c>
+      <c r="F65" t="s">
         <v>70</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G65" s="3">
         <v>46132</v>
       </c>
-      <c r="H44" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" s="4"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+      <c r="H65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B66" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="C66" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F45" s="4" t="s">
+      <c r="E66" t="s">
+        <v>64</v>
+      </c>
+      <c r="F66" t="s">
         <v>70</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G66" s="3">
         <v>46134</v>
       </c>
-      <c r="H45" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" s="4"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="H66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B67" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="C67" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" t="s">
         <v>77</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F46" s="4" t="s">
+      <c r="E67" t="s">
+        <v>64</v>
+      </c>
+      <c r="F67" t="s">
         <v>70</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G67" s="3">
         <v>46139</v>
       </c>
-      <c r="H46" s="4" t="b">
+      <c r="H67" t="b">
         <v>1</v>
       </c>
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G47" s="6">
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>114</v>
+      </c>
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D68" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" t="s">
+        <v>64</v>
+      </c>
+      <c r="F68" t="s">
+        <v>75</v>
+      </c>
+      <c r="G68" s="3">
+        <v>46139</v>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" t="s">
+        <v>77</v>
+      </c>
+      <c r="E69" t="s">
+        <v>64</v>
+      </c>
+      <c r="F69" t="s">
+        <v>75</v>
+      </c>
+      <c r="G69" s="3">
         <v>46132</v>
       </c>
-      <c r="H47" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G48" s="6">
+      <c r="H69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>116</v>
+      </c>
+      <c r="B70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" t="s">
+        <v>64</v>
+      </c>
+      <c r="F70" t="s">
+        <v>75</v>
+      </c>
+      <c r="G70" s="3">
         <v>46134</v>
       </c>
-      <c r="H48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G49" s="6">
-        <v>46139</v>
-      </c>
-      <c r="H49" s="4" t="b">
+      <c r="H70" t="b">
         <v>1</v>
       </c>
-      <c r="I49" s="4"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G50" s="6">
-        <v>46132</v>
-      </c>
-      <c r="H50" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G51" s="6">
-        <v>46134</v>
-      </c>
-      <c r="H51" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="4"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G52" s="6">
-        <v>46139</v>
-      </c>
-      <c r="H52" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G53" s="6">
-        <v>46132</v>
-      </c>
-      <c r="H53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" s="4"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G54" s="6">
-        <v>46134</v>
-      </c>
-      <c r="H54" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" s="4"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G55" s="6">
-        <v>46139</v>
-      </c>
-      <c r="H55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I55" s="4"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G56" s="6">
-        <v>46132</v>
-      </c>
-      <c r="H56" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G57" s="6">
-        <v>46134</v>
-      </c>
-      <c r="H57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" s="4"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G58" s="6">
-        <v>46139</v>
-      </c>
-      <c r="H58" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G59" s="6">
-        <v>46132</v>
-      </c>
-      <c r="H59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" s="4"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G60" s="6">
-        <v>46134</v>
-      </c>
-      <c r="H60" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" s="4"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G61" s="6">
-        <v>46139</v>
-      </c>
-      <c r="H61" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C62" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G62" s="6">
-        <v>46132</v>
-      </c>
-      <c r="H62" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" s="4"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G63" s="6">
-        <v>46134</v>
-      </c>
-      <c r="H63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I63" s="4"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G64" s="6">
-        <v>46139</v>
-      </c>
-      <c r="H64" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I64" s="4"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G65" s="6">
-        <v>46132</v>
-      </c>
-      <c r="H65" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" s="4"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G66" s="6">
-        <v>46134</v>
-      </c>
-      <c r="H66" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I66" s="4"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G67" s="6">
-        <v>46139</v>
-      </c>
-      <c r="H67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C68" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G68" s="6">
-        <v>46139</v>
-      </c>
-      <c r="H68" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I68" s="4"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C69" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G69" s="6">
-        <v>46132</v>
-      </c>
-      <c r="H69" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I69" s="4"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>FED0</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G70" s="6">
-        <v>46134</v>
-      </c>
-      <c r="H70" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I70" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G40">
-    <sortCondition ref="E2:E40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:H70">
+    <sortCondition ref="D41:D70"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
